--- a/dataproduct.api/wwwroot/templates/HRC2_BBGN_PhoiTam.xlsx
+++ b/dataproduct.api/wwwroot/templates/HRC2_BBGN_PhoiTam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Projects\BIEUMAU_SANXUAT\Source\dataproduct.BE\dataproduct.api\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C059D3E-C7CA-4C99-85CA-21BF73FFD5D0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99919E29-6BF0-4A82-AFB1-950EA98A8E3A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24720" windowHeight="11805" xr2:uid="{8D26054B-D371-44B9-99F0-3A3B1380D846}"/>
   </bookViews>
@@ -237,184 +237,45 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>11206</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>67235</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>356907</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1187512</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:rowOff>186118</xdr:rowOff>
     </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="5" name="Group 3">
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{976BAF94-83FC-4DC9-B6CA-321EF35DD714}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC4E37A1-A30F-4ADA-8AB8-95E1B031E7EC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGrpSpPr>
-          <a:grpSpLocks noChangeAspect="1"/>
-        </xdr:cNvGrpSpPr>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2250701" cy="795618"/>
-          <a:chOff x="0" y="1"/>
-          <a:chExt cx="2095500" cy="876300"/>
+          <a:off x="11206" y="67235"/>
+          <a:ext cx="1781424" cy="724001"/>
         </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="6" name="Picture 6">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26A0C954-C2D4-46A6-87B3-19A59D284078}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-            <a:extLst>
-              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-              </a:ext>
-            </a:extLst>
-          </a:blip>
-          <a:srcRect/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="133350" y="1"/>
-            <a:ext cx="1819275" cy="407343"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:solidFill>
-                  <a:srgbClr val="FFFFFF"/>
-                </a:solidFill>
-              </a14:hiddenFill>
-            </a:ext>
-            <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-              <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:miter lim="800000"/>
-                <a:headEnd/>
-                <a:tailEnd/>
-              </a14:hiddenLine>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="7" name="TextBox 4">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14FDA956-39EE-4520-9E62-1C3DA85F10F1}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1">
-            <a:spLocks noChangeArrowheads="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="0" y="382217"/>
-            <a:ext cx="2095500" cy="494084"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:txBody>
-          <a:bodyPr rot="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" anchor="ctr" anchorCtr="0" upright="1">
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr marL="0" marR="0" algn="ctr">
-              <a:lnSpc>
-                <a:spcPts val="1200"/>
-              </a:lnSpc>
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="800"/>
-              </a:spcAft>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>CÔNG TY CỔ PHẦN THÉP</a:t>
-            </a:r>
-            <a:br>
-              <a:rPr lang="en-US" sz="1200" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-            </a:br>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>HÒA PHÁT DUNG QUẤT</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>

--- a/dataproduct.api/wwwroot/templates/HRC2_BBGN_PhoiTam.xlsx
+++ b/dataproduct.api/wwwroot/templates/HRC2_BBGN_PhoiTam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Projects\BIEUMAU_SANXUAT\Source\dataproduct.BE\dataproduct.api\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99919E29-6BF0-4A82-AFB1-950EA98A8E3A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6DC211-33A6-4B06-AB4E-32EF4C0FFF8C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24720" windowHeight="11805" xr2:uid="{8D26054B-D371-44B9-99F0-3A3B1380D846}"/>
   </bookViews>

--- a/dataproduct.api/wwwroot/templates/HRC2_BBGN_PhoiTam.xlsx
+++ b/dataproduct.api/wwwroot/templates/HRC2_BBGN_PhoiTam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Projects\BIEUMAU_SANXUAT\Source\dataproduct.BE\dataproduct.api\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6DC211-33A6-4B06-AB4E-32EF4C0FFF8C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A87E844-9B3C-4DAE-A954-AA9B1575D0A6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24720" windowHeight="11805" xr2:uid="{8D26054B-D371-44B9-99F0-3A3B1380D846}"/>
   </bookViews>
